--- a/teacher_import_template.xlsx
+++ b/teacher_import_template.xlsx
@@ -1,13 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="المعلمين" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="المعلمين" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="قوائم" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet name="تعليمات" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,16 +27,77 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="008A90A0"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="0022358A"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00141B34"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00141B34"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0022358A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="005B6275"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EEF0F4"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +105,67 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D9D2C3"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D9D2C3"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D2C3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D2C3"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -122,6 +240,31 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>جود</author>
+  </authors>
+  <commentList>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>8 أرقام بدون مفتاح الدولة، مثال: 92345678</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>لا تكتب هنا: يُنشأ رقم فريد من 6 أرقام تلقائيًا عند الاستيراد.</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <t>لا تكتب هنا: الرقم السري يُعيَّن تلقائيًا 123456 عند إنشاء الحساب.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -413,70 +556,5145 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F301"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>اسم المعلم</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>رقم الهاتف</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>الصف</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>الشعبة</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>اسم المستخدم</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>الرقم السري</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="n"/>
+      <c r="B2" s="4" t="n"/>
+      <c r="C2" s="5" t="n"/>
+      <c r="D2" s="5" t="n"/>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n"/>
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="n"/>
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n"/>
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n"/>
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n"/>
+      <c r="B7" s="4" t="n"/>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n"/>
+      <c r="B8" s="4" t="n"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n"/>
+      <c r="B9" s="4" t="n"/>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n"/>
+      <c r="B10" s="4" t="n"/>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n"/>
+      <c r="B11" s="4" t="n"/>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n"/>
+      <c r="B12" s="4" t="n"/>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n"/>
+      <c r="B13" s="4" t="n"/>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n"/>
+      <c r="B14" s="4" t="n"/>
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n"/>
+      <c r="B15" s="4" t="n"/>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="n"/>
+      <c r="B16" s="4" t="n"/>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n"/>
+      <c r="B17" s="4" t="n"/>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="n"/>
+      <c r="B18" s="4" t="n"/>
+      <c r="C18" s="5" t="n"/>
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n"/>
+      <c r="B19" s="4" t="n"/>
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="n"/>
+      <c r="B20" s="4" t="n"/>
+      <c r="C20" s="5" t="n"/>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n"/>
+      <c r="B21" s="4" t="n"/>
+      <c r="C21" s="5" t="n"/>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="n"/>
+      <c r="B22" s="4" t="n"/>
+      <c r="C22" s="5" t="n"/>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n"/>
+      <c r="B23" s="4" t="n"/>
+      <c r="C23" s="5" t="n"/>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="n"/>
+      <c r="B24" s="4" t="n"/>
+      <c r="C24" s="5" t="n"/>
+      <c r="D24" s="5" t="n"/>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n"/>
+      <c r="B25" s="4" t="n"/>
+      <c r="C25" s="5" t="n"/>
+      <c r="D25" s="5" t="n"/>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="n"/>
+      <c r="B26" s="4" t="n"/>
+      <c r="C26" s="5" t="n"/>
+      <c r="D26" s="5" t="n"/>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n"/>
+      <c r="B27" s="4" t="n"/>
+      <c r="C27" s="5" t="n"/>
+      <c r="D27" s="5" t="n"/>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="n"/>
+      <c r="B28" s="4" t="n"/>
+      <c r="C28" s="5" t="n"/>
+      <c r="D28" s="5" t="n"/>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n"/>
+      <c r="B29" s="4" t="n"/>
+      <c r="C29" s="5" t="n"/>
+      <c r="D29" s="5" t="n"/>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="n"/>
+      <c r="B30" s="4" t="n"/>
+      <c r="C30" s="5" t="n"/>
+      <c r="D30" s="5" t="n"/>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="n"/>
+      <c r="B31" s="4" t="n"/>
+      <c r="C31" s="5" t="n"/>
+      <c r="D31" s="5" t="n"/>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="n"/>
+      <c r="B32" s="4" t="n"/>
+      <c r="C32" s="5" t="n"/>
+      <c r="D32" s="5" t="n"/>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n"/>
+      <c r="B33" s="4" t="n"/>
+      <c r="C33" s="5" t="n"/>
+      <c r="D33" s="5" t="n"/>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="n"/>
+      <c r="B34" s="4" t="n"/>
+      <c r="C34" s="5" t="n"/>
+      <c r="D34" s="5" t="n"/>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n"/>
+      <c r="B35" s="4" t="n"/>
+      <c r="C35" s="5" t="n"/>
+      <c r="D35" s="5" t="n"/>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="n"/>
+      <c r="B36" s="4" t="n"/>
+      <c r="C36" s="5" t="n"/>
+      <c r="D36" s="5" t="n"/>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="n"/>
+      <c r="B37" s="4" t="n"/>
+      <c r="C37" s="5" t="n"/>
+      <c r="D37" s="5" t="n"/>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="n"/>
+      <c r="B38" s="4" t="n"/>
+      <c r="C38" s="5" t="n"/>
+      <c r="D38" s="5" t="n"/>
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F38" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="n"/>
+      <c r="B39" s="4" t="n"/>
+      <c r="C39" s="5" t="n"/>
+      <c r="D39" s="5" t="n"/>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="n"/>
+      <c r="B40" s="4" t="n"/>
+      <c r="C40" s="5" t="n"/>
+      <c r="D40" s="5" t="n"/>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="n"/>
+      <c r="B41" s="4" t="n"/>
+      <c r="C41" s="5" t="n"/>
+      <c r="D41" s="5" t="n"/>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F41" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="n"/>
+      <c r="B42" s="4" t="n"/>
+      <c r="C42" s="5" t="n"/>
+      <c r="D42" s="5" t="n"/>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F42" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="n"/>
+      <c r="B43" s="4" t="n"/>
+      <c r="C43" s="5" t="n"/>
+      <c r="D43" s="5" t="n"/>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F43" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="n"/>
+      <c r="B44" s="4" t="n"/>
+      <c r="C44" s="5" t="n"/>
+      <c r="D44" s="5" t="n"/>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="n"/>
+      <c r="B45" s="4" t="n"/>
+      <c r="C45" s="5" t="n"/>
+      <c r="D45" s="5" t="n"/>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="n"/>
+      <c r="B46" s="4" t="n"/>
+      <c r="C46" s="5" t="n"/>
+      <c r="D46" s="5" t="n"/>
+      <c r="E46" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F46" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="n"/>
+      <c r="B47" s="4" t="n"/>
+      <c r="C47" s="5" t="n"/>
+      <c r="D47" s="5" t="n"/>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F47" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="n"/>
+      <c r="B48" s="4" t="n"/>
+      <c r="C48" s="5" t="n"/>
+      <c r="D48" s="5" t="n"/>
+      <c r="E48" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F48" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="n"/>
+      <c r="B49" s="4" t="n"/>
+      <c r="C49" s="5" t="n"/>
+      <c r="D49" s="5" t="n"/>
+      <c r="E49" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F49" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="n"/>
+      <c r="B50" s="4" t="n"/>
+      <c r="C50" s="5" t="n"/>
+      <c r="D50" s="5" t="n"/>
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F50" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="n"/>
+      <c r="B51" s="4" t="n"/>
+      <c r="C51" s="5" t="n"/>
+      <c r="D51" s="5" t="n"/>
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F51" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="n"/>
+      <c r="B52" s="4" t="n"/>
+      <c r="C52" s="5" t="n"/>
+      <c r="D52" s="5" t="n"/>
+      <c r="E52" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F52" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="n"/>
+      <c r="B53" s="4" t="n"/>
+      <c r="C53" s="5" t="n"/>
+      <c r="D53" s="5" t="n"/>
+      <c r="E53" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F53" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="n"/>
+      <c r="B54" s="4" t="n"/>
+      <c r="C54" s="5" t="n"/>
+      <c r="D54" s="5" t="n"/>
+      <c r="E54" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F54" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="n"/>
+      <c r="B55" s="4" t="n"/>
+      <c r="C55" s="5" t="n"/>
+      <c r="D55" s="5" t="n"/>
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F55" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="n"/>
+      <c r="B56" s="4" t="n"/>
+      <c r="C56" s="5" t="n"/>
+      <c r="D56" s="5" t="n"/>
+      <c r="E56" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F56" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="n"/>
+      <c r="B57" s="4" t="n"/>
+      <c r="C57" s="5" t="n"/>
+      <c r="D57" s="5" t="n"/>
+      <c r="E57" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F57" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="n"/>
+      <c r="B58" s="4" t="n"/>
+      <c r="C58" s="5" t="n"/>
+      <c r="D58" s="5" t="n"/>
+      <c r="E58" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F58" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="n"/>
+      <c r="B59" s="4" t="n"/>
+      <c r="C59" s="5" t="n"/>
+      <c r="D59" s="5" t="n"/>
+      <c r="E59" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F59" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="n"/>
+      <c r="B60" s="4" t="n"/>
+      <c r="C60" s="5" t="n"/>
+      <c r="D60" s="5" t="n"/>
+      <c r="E60" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F60" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="n"/>
+      <c r="B61" s="4" t="n"/>
+      <c r="C61" s="5" t="n"/>
+      <c r="D61" s="5" t="n"/>
+      <c r="E61" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F61" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="n"/>
+      <c r="B62" s="4" t="n"/>
+      <c r="C62" s="5" t="n"/>
+      <c r="D62" s="5" t="n"/>
+      <c r="E62" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F62" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="n"/>
+      <c r="B63" s="4" t="n"/>
+      <c r="C63" s="5" t="n"/>
+      <c r="D63" s="5" t="n"/>
+      <c r="E63" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F63" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="n"/>
+      <c r="B64" s="4" t="n"/>
+      <c r="C64" s="5" t="n"/>
+      <c r="D64" s="5" t="n"/>
+      <c r="E64" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F64" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="n"/>
+      <c r="B65" s="4" t="n"/>
+      <c r="C65" s="5" t="n"/>
+      <c r="D65" s="5" t="n"/>
+      <c r="E65" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F65" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="n"/>
+      <c r="B66" s="4" t="n"/>
+      <c r="C66" s="5" t="n"/>
+      <c r="D66" s="5" t="n"/>
+      <c r="E66" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F66" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="n"/>
+      <c r="B67" s="4" t="n"/>
+      <c r="C67" s="5" t="n"/>
+      <c r="D67" s="5" t="n"/>
+      <c r="E67" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F67" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="n"/>
+      <c r="B68" s="4" t="n"/>
+      <c r="C68" s="5" t="n"/>
+      <c r="D68" s="5" t="n"/>
+      <c r="E68" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F68" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="n"/>
+      <c r="B69" s="4" t="n"/>
+      <c r="C69" s="5" t="n"/>
+      <c r="D69" s="5" t="n"/>
+      <c r="E69" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F69" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="n"/>
+      <c r="B70" s="4" t="n"/>
+      <c r="C70" s="5" t="n"/>
+      <c r="D70" s="5" t="n"/>
+      <c r="E70" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F70" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="n"/>
+      <c r="B71" s="4" t="n"/>
+      <c r="C71" s="5" t="n"/>
+      <c r="D71" s="5" t="n"/>
+      <c r="E71" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F71" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="n"/>
+      <c r="B72" s="4" t="n"/>
+      <c r="C72" s="5" t="n"/>
+      <c r="D72" s="5" t="n"/>
+      <c r="E72" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F72" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="n"/>
+      <c r="B73" s="4" t="n"/>
+      <c r="C73" s="5" t="n"/>
+      <c r="D73" s="5" t="n"/>
+      <c r="E73" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F73" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="n"/>
+      <c r="B74" s="4" t="n"/>
+      <c r="C74" s="5" t="n"/>
+      <c r="D74" s="5" t="n"/>
+      <c r="E74" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F74" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="n"/>
+      <c r="B75" s="4" t="n"/>
+      <c r="C75" s="5" t="n"/>
+      <c r="D75" s="5" t="n"/>
+      <c r="E75" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F75" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="n"/>
+      <c r="B76" s="4" t="n"/>
+      <c r="C76" s="5" t="n"/>
+      <c r="D76" s="5" t="n"/>
+      <c r="E76" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F76" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="n"/>
+      <c r="B77" s="4" t="n"/>
+      <c r="C77" s="5" t="n"/>
+      <c r="D77" s="5" t="n"/>
+      <c r="E77" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F77" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="n"/>
+      <c r="B78" s="4" t="n"/>
+      <c r="C78" s="5" t="n"/>
+      <c r="D78" s="5" t="n"/>
+      <c r="E78" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F78" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="n"/>
+      <c r="B79" s="4" t="n"/>
+      <c r="C79" s="5" t="n"/>
+      <c r="D79" s="5" t="n"/>
+      <c r="E79" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F79" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="n"/>
+      <c r="B80" s="4" t="n"/>
+      <c r="C80" s="5" t="n"/>
+      <c r="D80" s="5" t="n"/>
+      <c r="E80" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F80" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="n"/>
+      <c r="B81" s="4" t="n"/>
+      <c r="C81" s="5" t="n"/>
+      <c r="D81" s="5" t="n"/>
+      <c r="E81" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F81" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="n"/>
+      <c r="B82" s="4" t="n"/>
+      <c r="C82" s="5" t="n"/>
+      <c r="D82" s="5" t="n"/>
+      <c r="E82" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F82" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="n"/>
+      <c r="B83" s="4" t="n"/>
+      <c r="C83" s="5" t="n"/>
+      <c r="D83" s="5" t="n"/>
+      <c r="E83" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F83" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="n"/>
+      <c r="B84" s="4" t="n"/>
+      <c r="C84" s="5" t="n"/>
+      <c r="D84" s="5" t="n"/>
+      <c r="E84" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F84" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="n"/>
+      <c r="B85" s="4" t="n"/>
+      <c r="C85" s="5" t="n"/>
+      <c r="D85" s="5" t="n"/>
+      <c r="E85" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F85" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="n"/>
+      <c r="B86" s="4" t="n"/>
+      <c r="C86" s="5" t="n"/>
+      <c r="D86" s="5" t="n"/>
+      <c r="E86" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F86" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="n"/>
+      <c r="B87" s="4" t="n"/>
+      <c r="C87" s="5" t="n"/>
+      <c r="D87" s="5" t="n"/>
+      <c r="E87" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F87" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="n"/>
+      <c r="B88" s="4" t="n"/>
+      <c r="C88" s="5" t="n"/>
+      <c r="D88" s="5" t="n"/>
+      <c r="E88" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F88" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="n"/>
+      <c r="B89" s="4" t="n"/>
+      <c r="C89" s="5" t="n"/>
+      <c r="D89" s="5" t="n"/>
+      <c r="E89" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F89" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="n"/>
+      <c r="B90" s="4" t="n"/>
+      <c r="C90" s="5" t="n"/>
+      <c r="D90" s="5" t="n"/>
+      <c r="E90" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F90" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="n"/>
+      <c r="B91" s="4" t="n"/>
+      <c r="C91" s="5" t="n"/>
+      <c r="D91" s="5" t="n"/>
+      <c r="E91" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F91" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="n"/>
+      <c r="B92" s="4" t="n"/>
+      <c r="C92" s="5" t="n"/>
+      <c r="D92" s="5" t="n"/>
+      <c r="E92" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F92" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="n"/>
+      <c r="B93" s="4" t="n"/>
+      <c r="C93" s="5" t="n"/>
+      <c r="D93" s="5" t="n"/>
+      <c r="E93" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F93" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="n"/>
+      <c r="B94" s="4" t="n"/>
+      <c r="C94" s="5" t="n"/>
+      <c r="D94" s="5" t="n"/>
+      <c r="E94" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F94" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="n"/>
+      <c r="B95" s="4" t="n"/>
+      <c r="C95" s="5" t="n"/>
+      <c r="D95" s="5" t="n"/>
+      <c r="E95" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F95" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="n"/>
+      <c r="B96" s="4" t="n"/>
+      <c r="C96" s="5" t="n"/>
+      <c r="D96" s="5" t="n"/>
+      <c r="E96" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F96" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="n"/>
+      <c r="B97" s="4" t="n"/>
+      <c r="C97" s="5" t="n"/>
+      <c r="D97" s="5" t="n"/>
+      <c r="E97" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F97" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="3" t="n"/>
+      <c r="B98" s="4" t="n"/>
+      <c r="C98" s="5" t="n"/>
+      <c r="D98" s="5" t="n"/>
+      <c r="E98" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F98" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="n"/>
+      <c r="B99" s="4" t="n"/>
+      <c r="C99" s="5" t="n"/>
+      <c r="D99" s="5" t="n"/>
+      <c r="E99" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F99" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="3" t="n"/>
+      <c r="B100" s="4" t="n"/>
+      <c r="C100" s="5" t="n"/>
+      <c r="D100" s="5" t="n"/>
+      <c r="E100" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F100" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="n"/>
+      <c r="B101" s="4" t="n"/>
+      <c r="C101" s="5" t="n"/>
+      <c r="D101" s="5" t="n"/>
+      <c r="E101" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F101" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="3" t="n"/>
+      <c r="B102" s="4" t="n"/>
+      <c r="C102" s="5" t="n"/>
+      <c r="D102" s="5" t="n"/>
+      <c r="E102" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F102" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="n"/>
+      <c r="B103" s="4" t="n"/>
+      <c r="C103" s="5" t="n"/>
+      <c r="D103" s="5" t="n"/>
+      <c r="E103" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F103" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="3" t="n"/>
+      <c r="B104" s="4" t="n"/>
+      <c r="C104" s="5" t="n"/>
+      <c r="D104" s="5" t="n"/>
+      <c r="E104" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F104" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="3" t="n"/>
+      <c r="B105" s="4" t="n"/>
+      <c r="C105" s="5" t="n"/>
+      <c r="D105" s="5" t="n"/>
+      <c r="E105" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F105" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="3" t="n"/>
+      <c r="B106" s="4" t="n"/>
+      <c r="C106" s="5" t="n"/>
+      <c r="D106" s="5" t="n"/>
+      <c r="E106" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F106" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="3" t="n"/>
+      <c r="B107" s="4" t="n"/>
+      <c r="C107" s="5" t="n"/>
+      <c r="D107" s="5" t="n"/>
+      <c r="E107" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F107" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="3" t="n"/>
+      <c r="B108" s="4" t="n"/>
+      <c r="C108" s="5" t="n"/>
+      <c r="D108" s="5" t="n"/>
+      <c r="E108" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F108" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="3" t="n"/>
+      <c r="B109" s="4" t="n"/>
+      <c r="C109" s="5" t="n"/>
+      <c r="D109" s="5" t="n"/>
+      <c r="E109" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F109" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="3" t="n"/>
+      <c r="B110" s="4" t="n"/>
+      <c r="C110" s="5" t="n"/>
+      <c r="D110" s="5" t="n"/>
+      <c r="E110" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F110" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="3" t="n"/>
+      <c r="B111" s="4" t="n"/>
+      <c r="C111" s="5" t="n"/>
+      <c r="D111" s="5" t="n"/>
+      <c r="E111" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F111" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="3" t="n"/>
+      <c r="B112" s="4" t="n"/>
+      <c r="C112" s="5" t="n"/>
+      <c r="D112" s="5" t="n"/>
+      <c r="E112" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F112" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="3" t="n"/>
+      <c r="B113" s="4" t="n"/>
+      <c r="C113" s="5" t="n"/>
+      <c r="D113" s="5" t="n"/>
+      <c r="E113" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F113" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="3" t="n"/>
+      <c r="B114" s="4" t="n"/>
+      <c r="C114" s="5" t="n"/>
+      <c r="D114" s="5" t="n"/>
+      <c r="E114" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F114" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="3" t="n"/>
+      <c r="B115" s="4" t="n"/>
+      <c r="C115" s="5" t="n"/>
+      <c r="D115" s="5" t="n"/>
+      <c r="E115" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F115" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="3" t="n"/>
+      <c r="B116" s="4" t="n"/>
+      <c r="C116" s="5" t="n"/>
+      <c r="D116" s="5" t="n"/>
+      <c r="E116" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F116" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="3" t="n"/>
+      <c r="B117" s="4" t="n"/>
+      <c r="C117" s="5" t="n"/>
+      <c r="D117" s="5" t="n"/>
+      <c r="E117" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F117" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="3" t="n"/>
+      <c r="B118" s="4" t="n"/>
+      <c r="C118" s="5" t="n"/>
+      <c r="D118" s="5" t="n"/>
+      <c r="E118" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F118" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="3" t="n"/>
+      <c r="B119" s="4" t="n"/>
+      <c r="C119" s="5" t="n"/>
+      <c r="D119" s="5" t="n"/>
+      <c r="E119" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F119" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="3" t="n"/>
+      <c r="B120" s="4" t="n"/>
+      <c r="C120" s="5" t="n"/>
+      <c r="D120" s="5" t="n"/>
+      <c r="E120" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F120" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="3" t="n"/>
+      <c r="B121" s="4" t="n"/>
+      <c r="C121" s="5" t="n"/>
+      <c r="D121" s="5" t="n"/>
+      <c r="E121" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F121" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="3" t="n"/>
+      <c r="B122" s="4" t="n"/>
+      <c r="C122" s="5" t="n"/>
+      <c r="D122" s="5" t="n"/>
+      <c r="E122" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F122" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="3" t="n"/>
+      <c r="B123" s="4" t="n"/>
+      <c r="C123" s="5" t="n"/>
+      <c r="D123" s="5" t="n"/>
+      <c r="E123" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F123" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="3" t="n"/>
+      <c r="B124" s="4" t="n"/>
+      <c r="C124" s="5" t="n"/>
+      <c r="D124" s="5" t="n"/>
+      <c r="E124" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F124" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="3" t="n"/>
+      <c r="B125" s="4" t="n"/>
+      <c r="C125" s="5" t="n"/>
+      <c r="D125" s="5" t="n"/>
+      <c r="E125" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F125" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="3" t="n"/>
+      <c r="B126" s="4" t="n"/>
+      <c r="C126" s="5" t="n"/>
+      <c r="D126" s="5" t="n"/>
+      <c r="E126" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F126" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="3" t="n"/>
+      <c r="B127" s="4" t="n"/>
+      <c r="C127" s="5" t="n"/>
+      <c r="D127" s="5" t="n"/>
+      <c r="E127" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F127" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="3" t="n"/>
+      <c r="B128" s="4" t="n"/>
+      <c r="C128" s="5" t="n"/>
+      <c r="D128" s="5" t="n"/>
+      <c r="E128" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F128" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="3" t="n"/>
+      <c r="B129" s="4" t="n"/>
+      <c r="C129" s="5" t="n"/>
+      <c r="D129" s="5" t="n"/>
+      <c r="E129" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F129" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="3" t="n"/>
+      <c r="B130" s="4" t="n"/>
+      <c r="C130" s="5" t="n"/>
+      <c r="D130" s="5" t="n"/>
+      <c r="E130" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F130" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="3" t="n"/>
+      <c r="B131" s="4" t="n"/>
+      <c r="C131" s="5" t="n"/>
+      <c r="D131" s="5" t="n"/>
+      <c r="E131" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F131" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="3" t="n"/>
+      <c r="B132" s="4" t="n"/>
+      <c r="C132" s="5" t="n"/>
+      <c r="D132" s="5" t="n"/>
+      <c r="E132" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F132" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="3" t="n"/>
+      <c r="B133" s="4" t="n"/>
+      <c r="C133" s="5" t="n"/>
+      <c r="D133" s="5" t="n"/>
+      <c r="E133" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F133" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="3" t="n"/>
+      <c r="B134" s="4" t="n"/>
+      <c r="C134" s="5" t="n"/>
+      <c r="D134" s="5" t="n"/>
+      <c r="E134" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F134" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="3" t="n"/>
+      <c r="B135" s="4" t="n"/>
+      <c r="C135" s="5" t="n"/>
+      <c r="D135" s="5" t="n"/>
+      <c r="E135" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F135" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="3" t="n"/>
+      <c r="B136" s="4" t="n"/>
+      <c r="C136" s="5" t="n"/>
+      <c r="D136" s="5" t="n"/>
+      <c r="E136" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F136" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="3" t="n"/>
+      <c r="B137" s="4" t="n"/>
+      <c r="C137" s="5" t="n"/>
+      <c r="D137" s="5" t="n"/>
+      <c r="E137" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F137" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="3" t="n"/>
+      <c r="B138" s="4" t="n"/>
+      <c r="C138" s="5" t="n"/>
+      <c r="D138" s="5" t="n"/>
+      <c r="E138" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F138" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="3" t="n"/>
+      <c r="B139" s="4" t="n"/>
+      <c r="C139" s="5" t="n"/>
+      <c r="D139" s="5" t="n"/>
+      <c r="E139" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F139" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="3" t="n"/>
+      <c r="B140" s="4" t="n"/>
+      <c r="C140" s="5" t="n"/>
+      <c r="D140" s="5" t="n"/>
+      <c r="E140" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F140" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="3" t="n"/>
+      <c r="B141" s="4" t="n"/>
+      <c r="C141" s="5" t="n"/>
+      <c r="D141" s="5" t="n"/>
+      <c r="E141" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F141" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="3" t="n"/>
+      <c r="B142" s="4" t="n"/>
+      <c r="C142" s="5" t="n"/>
+      <c r="D142" s="5" t="n"/>
+      <c r="E142" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F142" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="3" t="n"/>
+      <c r="B143" s="4" t="n"/>
+      <c r="C143" s="5" t="n"/>
+      <c r="D143" s="5" t="n"/>
+      <c r="E143" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F143" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="3" t="n"/>
+      <c r="B144" s="4" t="n"/>
+      <c r="C144" s="5" t="n"/>
+      <c r="D144" s="5" t="n"/>
+      <c r="E144" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F144" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="3" t="n"/>
+      <c r="B145" s="4" t="n"/>
+      <c r="C145" s="5" t="n"/>
+      <c r="D145" s="5" t="n"/>
+      <c r="E145" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F145" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="3" t="n"/>
+      <c r="B146" s="4" t="n"/>
+      <c r="C146" s="5" t="n"/>
+      <c r="D146" s="5" t="n"/>
+      <c r="E146" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F146" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="3" t="n"/>
+      <c r="B147" s="4" t="n"/>
+      <c r="C147" s="5" t="n"/>
+      <c r="D147" s="5" t="n"/>
+      <c r="E147" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F147" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="3" t="n"/>
+      <c r="B148" s="4" t="n"/>
+      <c r="C148" s="5" t="n"/>
+      <c r="D148" s="5" t="n"/>
+      <c r="E148" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F148" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="3" t="n"/>
+      <c r="B149" s="4" t="n"/>
+      <c r="C149" s="5" t="n"/>
+      <c r="D149" s="5" t="n"/>
+      <c r="E149" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F149" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="3" t="n"/>
+      <c r="B150" s="4" t="n"/>
+      <c r="C150" s="5" t="n"/>
+      <c r="D150" s="5" t="n"/>
+      <c r="E150" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F150" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="3" t="n"/>
+      <c r="B151" s="4" t="n"/>
+      <c r="C151" s="5" t="n"/>
+      <c r="D151" s="5" t="n"/>
+      <c r="E151" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F151" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="3" t="n"/>
+      <c r="B152" s="4" t="n"/>
+      <c r="C152" s="5" t="n"/>
+      <c r="D152" s="5" t="n"/>
+      <c r="E152" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F152" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="3" t="n"/>
+      <c r="B153" s="4" t="n"/>
+      <c r="C153" s="5" t="n"/>
+      <c r="D153" s="5" t="n"/>
+      <c r="E153" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F153" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="3" t="n"/>
+      <c r="B154" s="4" t="n"/>
+      <c r="C154" s="5" t="n"/>
+      <c r="D154" s="5" t="n"/>
+      <c r="E154" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F154" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="3" t="n"/>
+      <c r="B155" s="4" t="n"/>
+      <c r="C155" s="5" t="n"/>
+      <c r="D155" s="5" t="n"/>
+      <c r="E155" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F155" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="3" t="n"/>
+      <c r="B156" s="4" t="n"/>
+      <c r="C156" s="5" t="n"/>
+      <c r="D156" s="5" t="n"/>
+      <c r="E156" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F156" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="3" t="n"/>
+      <c r="B157" s="4" t="n"/>
+      <c r="C157" s="5" t="n"/>
+      <c r="D157" s="5" t="n"/>
+      <c r="E157" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F157" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="3" t="n"/>
+      <c r="B158" s="4" t="n"/>
+      <c r="C158" s="5" t="n"/>
+      <c r="D158" s="5" t="n"/>
+      <c r="E158" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F158" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="3" t="n"/>
+      <c r="B159" s="4" t="n"/>
+      <c r="C159" s="5" t="n"/>
+      <c r="D159" s="5" t="n"/>
+      <c r="E159" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F159" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="3" t="n"/>
+      <c r="B160" s="4" t="n"/>
+      <c r="C160" s="5" t="n"/>
+      <c r="D160" s="5" t="n"/>
+      <c r="E160" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F160" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="3" t="n"/>
+      <c r="B161" s="4" t="n"/>
+      <c r="C161" s="5" t="n"/>
+      <c r="D161" s="5" t="n"/>
+      <c r="E161" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F161" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="3" t="n"/>
+      <c r="B162" s="4" t="n"/>
+      <c r="C162" s="5" t="n"/>
+      <c r="D162" s="5" t="n"/>
+      <c r="E162" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F162" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="3" t="n"/>
+      <c r="B163" s="4" t="n"/>
+      <c r="C163" s="5" t="n"/>
+      <c r="D163" s="5" t="n"/>
+      <c r="E163" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F163" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="3" t="n"/>
+      <c r="B164" s="4" t="n"/>
+      <c r="C164" s="5" t="n"/>
+      <c r="D164" s="5" t="n"/>
+      <c r="E164" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F164" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="3" t="n"/>
+      <c r="B165" s="4" t="n"/>
+      <c r="C165" s="5" t="n"/>
+      <c r="D165" s="5" t="n"/>
+      <c r="E165" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F165" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="3" t="n"/>
+      <c r="B166" s="4" t="n"/>
+      <c r="C166" s="5" t="n"/>
+      <c r="D166" s="5" t="n"/>
+      <c r="E166" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F166" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="3" t="n"/>
+      <c r="B167" s="4" t="n"/>
+      <c r="C167" s="5" t="n"/>
+      <c r="D167" s="5" t="n"/>
+      <c r="E167" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F167" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="3" t="n"/>
+      <c r="B168" s="4" t="n"/>
+      <c r="C168" s="5" t="n"/>
+      <c r="D168" s="5" t="n"/>
+      <c r="E168" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F168" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="3" t="n"/>
+      <c r="B169" s="4" t="n"/>
+      <c r="C169" s="5" t="n"/>
+      <c r="D169" s="5" t="n"/>
+      <c r="E169" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F169" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="3" t="n"/>
+      <c r="B170" s="4" t="n"/>
+      <c r="C170" s="5" t="n"/>
+      <c r="D170" s="5" t="n"/>
+      <c r="E170" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F170" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="3" t="n"/>
+      <c r="B171" s="4" t="n"/>
+      <c r="C171" s="5" t="n"/>
+      <c r="D171" s="5" t="n"/>
+      <c r="E171" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F171" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="3" t="n"/>
+      <c r="B172" s="4" t="n"/>
+      <c r="C172" s="5" t="n"/>
+      <c r="D172" s="5" t="n"/>
+      <c r="E172" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F172" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="3" t="n"/>
+      <c r="B173" s="4" t="n"/>
+      <c r="C173" s="5" t="n"/>
+      <c r="D173" s="5" t="n"/>
+      <c r="E173" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F173" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="3" t="n"/>
+      <c r="B174" s="4" t="n"/>
+      <c r="C174" s="5" t="n"/>
+      <c r="D174" s="5" t="n"/>
+      <c r="E174" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F174" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="3" t="n"/>
+      <c r="B175" s="4" t="n"/>
+      <c r="C175" s="5" t="n"/>
+      <c r="D175" s="5" t="n"/>
+      <c r="E175" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F175" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="3" t="n"/>
+      <c r="B176" s="4" t="n"/>
+      <c r="C176" s="5" t="n"/>
+      <c r="D176" s="5" t="n"/>
+      <c r="E176" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F176" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="3" t="n"/>
+      <c r="B177" s="4" t="n"/>
+      <c r="C177" s="5" t="n"/>
+      <c r="D177" s="5" t="n"/>
+      <c r="E177" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F177" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="3" t="n"/>
+      <c r="B178" s="4" t="n"/>
+      <c r="C178" s="5" t="n"/>
+      <c r="D178" s="5" t="n"/>
+      <c r="E178" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F178" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="3" t="n"/>
+      <c r="B179" s="4" t="n"/>
+      <c r="C179" s="5" t="n"/>
+      <c r="D179" s="5" t="n"/>
+      <c r="E179" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F179" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="3" t="n"/>
+      <c r="B180" s="4" t="n"/>
+      <c r="C180" s="5" t="n"/>
+      <c r="D180" s="5" t="n"/>
+      <c r="E180" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F180" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="3" t="n"/>
+      <c r="B181" s="4" t="n"/>
+      <c r="C181" s="5" t="n"/>
+      <c r="D181" s="5" t="n"/>
+      <c r="E181" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F181" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="3" t="n"/>
+      <c r="B182" s="4" t="n"/>
+      <c r="C182" s="5" t="n"/>
+      <c r="D182" s="5" t="n"/>
+      <c r="E182" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F182" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="3" t="n"/>
+      <c r="B183" s="4" t="n"/>
+      <c r="C183" s="5" t="n"/>
+      <c r="D183" s="5" t="n"/>
+      <c r="E183" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F183" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="3" t="n"/>
+      <c r="B184" s="4" t="n"/>
+      <c r="C184" s="5" t="n"/>
+      <c r="D184" s="5" t="n"/>
+      <c r="E184" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F184" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="3" t="n"/>
+      <c r="B185" s="4" t="n"/>
+      <c r="C185" s="5" t="n"/>
+      <c r="D185" s="5" t="n"/>
+      <c r="E185" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F185" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="3" t="n"/>
+      <c r="B186" s="4" t="n"/>
+      <c r="C186" s="5" t="n"/>
+      <c r="D186" s="5" t="n"/>
+      <c r="E186" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F186" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="3" t="n"/>
+      <c r="B187" s="4" t="n"/>
+      <c r="C187" s="5" t="n"/>
+      <c r="D187" s="5" t="n"/>
+      <c r="E187" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F187" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="3" t="n"/>
+      <c r="B188" s="4" t="n"/>
+      <c r="C188" s="5" t="n"/>
+      <c r="D188" s="5" t="n"/>
+      <c r="E188" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F188" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="3" t="n"/>
+      <c r="B189" s="4" t="n"/>
+      <c r="C189" s="5" t="n"/>
+      <c r="D189" s="5" t="n"/>
+      <c r="E189" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F189" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="3" t="n"/>
+      <c r="B190" s="4" t="n"/>
+      <c r="C190" s="5" t="n"/>
+      <c r="D190" s="5" t="n"/>
+      <c r="E190" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F190" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="3" t="n"/>
+      <c r="B191" s="4" t="n"/>
+      <c r="C191" s="5" t="n"/>
+      <c r="D191" s="5" t="n"/>
+      <c r="E191" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F191" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="3" t="n"/>
+      <c r="B192" s="4" t="n"/>
+      <c r="C192" s="5" t="n"/>
+      <c r="D192" s="5" t="n"/>
+      <c r="E192" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F192" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="3" t="n"/>
+      <c r="B193" s="4" t="n"/>
+      <c r="C193" s="5" t="n"/>
+      <c r="D193" s="5" t="n"/>
+      <c r="E193" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F193" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="3" t="n"/>
+      <c r="B194" s="4" t="n"/>
+      <c r="C194" s="5" t="n"/>
+      <c r="D194" s="5" t="n"/>
+      <c r="E194" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F194" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="3" t="n"/>
+      <c r="B195" s="4" t="n"/>
+      <c r="C195" s="5" t="n"/>
+      <c r="D195" s="5" t="n"/>
+      <c r="E195" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F195" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="3" t="n"/>
+      <c r="B196" s="4" t="n"/>
+      <c r="C196" s="5" t="n"/>
+      <c r="D196" s="5" t="n"/>
+      <c r="E196" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F196" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="3" t="n"/>
+      <c r="B197" s="4" t="n"/>
+      <c r="C197" s="5" t="n"/>
+      <c r="D197" s="5" t="n"/>
+      <c r="E197" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F197" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="3" t="n"/>
+      <c r="B198" s="4" t="n"/>
+      <c r="C198" s="5" t="n"/>
+      <c r="D198" s="5" t="n"/>
+      <c r="E198" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F198" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="3" t="n"/>
+      <c r="B199" s="4" t="n"/>
+      <c r="C199" s="5" t="n"/>
+      <c r="D199" s="5" t="n"/>
+      <c r="E199" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F199" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="3" t="n"/>
+      <c r="B200" s="4" t="n"/>
+      <c r="C200" s="5" t="n"/>
+      <c r="D200" s="5" t="n"/>
+      <c r="E200" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F200" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="3" t="n"/>
+      <c r="B201" s="4" t="n"/>
+      <c r="C201" s="5" t="n"/>
+      <c r="D201" s="5" t="n"/>
+      <c r="E201" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F201" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="3" t="n"/>
+      <c r="B202" s="4" t="n"/>
+      <c r="C202" s="5" t="n"/>
+      <c r="D202" s="5" t="n"/>
+      <c r="E202" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F202" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="3" t="n"/>
+      <c r="B203" s="4" t="n"/>
+      <c r="C203" s="5" t="n"/>
+      <c r="D203" s="5" t="n"/>
+      <c r="E203" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F203" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="3" t="n"/>
+      <c r="B204" s="4" t="n"/>
+      <c r="C204" s="5" t="n"/>
+      <c r="D204" s="5" t="n"/>
+      <c r="E204" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F204" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="3" t="n"/>
+      <c r="B205" s="4" t="n"/>
+      <c r="C205" s="5" t="n"/>
+      <c r="D205" s="5" t="n"/>
+      <c r="E205" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F205" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="3" t="n"/>
+      <c r="B206" s="4" t="n"/>
+      <c r="C206" s="5" t="n"/>
+      <c r="D206" s="5" t="n"/>
+      <c r="E206" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F206" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="3" t="n"/>
+      <c r="B207" s="4" t="n"/>
+      <c r="C207" s="5" t="n"/>
+      <c r="D207" s="5" t="n"/>
+      <c r="E207" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F207" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="3" t="n"/>
+      <c r="B208" s="4" t="n"/>
+      <c r="C208" s="5" t="n"/>
+      <c r="D208" s="5" t="n"/>
+      <c r="E208" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F208" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="3" t="n"/>
+      <c r="B209" s="4" t="n"/>
+      <c r="C209" s="5" t="n"/>
+      <c r="D209" s="5" t="n"/>
+      <c r="E209" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F209" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="3" t="n"/>
+      <c r="B210" s="4" t="n"/>
+      <c r="C210" s="5" t="n"/>
+      <c r="D210" s="5" t="n"/>
+      <c r="E210" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F210" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="3" t="n"/>
+      <c r="B211" s="4" t="n"/>
+      <c r="C211" s="5" t="n"/>
+      <c r="D211" s="5" t="n"/>
+      <c r="E211" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F211" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="3" t="n"/>
+      <c r="B212" s="4" t="n"/>
+      <c r="C212" s="5" t="n"/>
+      <c r="D212" s="5" t="n"/>
+      <c r="E212" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F212" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="3" t="n"/>
+      <c r="B213" s="4" t="n"/>
+      <c r="C213" s="5" t="n"/>
+      <c r="D213" s="5" t="n"/>
+      <c r="E213" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F213" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="3" t="n"/>
+      <c r="B214" s="4" t="n"/>
+      <c r="C214" s="5" t="n"/>
+      <c r="D214" s="5" t="n"/>
+      <c r="E214" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F214" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="3" t="n"/>
+      <c r="B215" s="4" t="n"/>
+      <c r="C215" s="5" t="n"/>
+      <c r="D215" s="5" t="n"/>
+      <c r="E215" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F215" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="3" t="n"/>
+      <c r="B216" s="4" t="n"/>
+      <c r="C216" s="5" t="n"/>
+      <c r="D216" s="5" t="n"/>
+      <c r="E216" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F216" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="3" t="n"/>
+      <c r="B217" s="4" t="n"/>
+      <c r="C217" s="5" t="n"/>
+      <c r="D217" s="5" t="n"/>
+      <c r="E217" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F217" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="3" t="n"/>
+      <c r="B218" s="4" t="n"/>
+      <c r="C218" s="5" t="n"/>
+      <c r="D218" s="5" t="n"/>
+      <c r="E218" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F218" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="3" t="n"/>
+      <c r="B219" s="4" t="n"/>
+      <c r="C219" s="5" t="n"/>
+      <c r="D219" s="5" t="n"/>
+      <c r="E219" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F219" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="3" t="n"/>
+      <c r="B220" s="4" t="n"/>
+      <c r="C220" s="5" t="n"/>
+      <c r="D220" s="5" t="n"/>
+      <c r="E220" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F220" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="3" t="n"/>
+      <c r="B221" s="4" t="n"/>
+      <c r="C221" s="5" t="n"/>
+      <c r="D221" s="5" t="n"/>
+      <c r="E221" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F221" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="3" t="n"/>
+      <c r="B222" s="4" t="n"/>
+      <c r="C222" s="5" t="n"/>
+      <c r="D222" s="5" t="n"/>
+      <c r="E222" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F222" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="3" t="n"/>
+      <c r="B223" s="4" t="n"/>
+      <c r="C223" s="5" t="n"/>
+      <c r="D223" s="5" t="n"/>
+      <c r="E223" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F223" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="3" t="n"/>
+      <c r="B224" s="4" t="n"/>
+      <c r="C224" s="5" t="n"/>
+      <c r="D224" s="5" t="n"/>
+      <c r="E224" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F224" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="3" t="n"/>
+      <c r="B225" s="4" t="n"/>
+      <c r="C225" s="5" t="n"/>
+      <c r="D225" s="5" t="n"/>
+      <c r="E225" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F225" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="3" t="n"/>
+      <c r="B226" s="4" t="n"/>
+      <c r="C226" s="5" t="n"/>
+      <c r="D226" s="5" t="n"/>
+      <c r="E226" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F226" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="3" t="n"/>
+      <c r="B227" s="4" t="n"/>
+      <c r="C227" s="5" t="n"/>
+      <c r="D227" s="5" t="n"/>
+      <c r="E227" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F227" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="3" t="n"/>
+      <c r="B228" s="4" t="n"/>
+      <c r="C228" s="5" t="n"/>
+      <c r="D228" s="5" t="n"/>
+      <c r="E228" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F228" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="3" t="n"/>
+      <c r="B229" s="4" t="n"/>
+      <c r="C229" s="5" t="n"/>
+      <c r="D229" s="5" t="n"/>
+      <c r="E229" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F229" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="3" t="n"/>
+      <c r="B230" s="4" t="n"/>
+      <c r="C230" s="5" t="n"/>
+      <c r="D230" s="5" t="n"/>
+      <c r="E230" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F230" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="3" t="n"/>
+      <c r="B231" s="4" t="n"/>
+      <c r="C231" s="5" t="n"/>
+      <c r="D231" s="5" t="n"/>
+      <c r="E231" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F231" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="3" t="n"/>
+      <c r="B232" s="4" t="n"/>
+      <c r="C232" s="5" t="n"/>
+      <c r="D232" s="5" t="n"/>
+      <c r="E232" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F232" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="3" t="n"/>
+      <c r="B233" s="4" t="n"/>
+      <c r="C233" s="5" t="n"/>
+      <c r="D233" s="5" t="n"/>
+      <c r="E233" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F233" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="3" t="n"/>
+      <c r="B234" s="4" t="n"/>
+      <c r="C234" s="5" t="n"/>
+      <c r="D234" s="5" t="n"/>
+      <c r="E234" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F234" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="3" t="n"/>
+      <c r="B235" s="4" t="n"/>
+      <c r="C235" s="5" t="n"/>
+      <c r="D235" s="5" t="n"/>
+      <c r="E235" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F235" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="3" t="n"/>
+      <c r="B236" s="4" t="n"/>
+      <c r="C236" s="5" t="n"/>
+      <c r="D236" s="5" t="n"/>
+      <c r="E236" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F236" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="3" t="n"/>
+      <c r="B237" s="4" t="n"/>
+      <c r="C237" s="5" t="n"/>
+      <c r="D237" s="5" t="n"/>
+      <c r="E237" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F237" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="3" t="n"/>
+      <c r="B238" s="4" t="n"/>
+      <c r="C238" s="5" t="n"/>
+      <c r="D238" s="5" t="n"/>
+      <c r="E238" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F238" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="3" t="n"/>
+      <c r="B239" s="4" t="n"/>
+      <c r="C239" s="5" t="n"/>
+      <c r="D239" s="5" t="n"/>
+      <c r="E239" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F239" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="3" t="n"/>
+      <c r="B240" s="4" t="n"/>
+      <c r="C240" s="5" t="n"/>
+      <c r="D240" s="5" t="n"/>
+      <c r="E240" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F240" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="3" t="n"/>
+      <c r="B241" s="4" t="n"/>
+      <c r="C241" s="5" t="n"/>
+      <c r="D241" s="5" t="n"/>
+      <c r="E241" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F241" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="3" t="n"/>
+      <c r="B242" s="4" t="n"/>
+      <c r="C242" s="5" t="n"/>
+      <c r="D242" s="5" t="n"/>
+      <c r="E242" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F242" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="3" t="n"/>
+      <c r="B243" s="4" t="n"/>
+      <c r="C243" s="5" t="n"/>
+      <c r="D243" s="5" t="n"/>
+      <c r="E243" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F243" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="3" t="n"/>
+      <c r="B244" s="4" t="n"/>
+      <c r="C244" s="5" t="n"/>
+      <c r="D244" s="5" t="n"/>
+      <c r="E244" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F244" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="3" t="n"/>
+      <c r="B245" s="4" t="n"/>
+      <c r="C245" s="5" t="n"/>
+      <c r="D245" s="5" t="n"/>
+      <c r="E245" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F245" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="3" t="n"/>
+      <c r="B246" s="4" t="n"/>
+      <c r="C246" s="5" t="n"/>
+      <c r="D246" s="5" t="n"/>
+      <c r="E246" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F246" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="3" t="n"/>
+      <c r="B247" s="4" t="n"/>
+      <c r="C247" s="5" t="n"/>
+      <c r="D247" s="5" t="n"/>
+      <c r="E247" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F247" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="3" t="n"/>
+      <c r="B248" s="4" t="n"/>
+      <c r="C248" s="5" t="n"/>
+      <c r="D248" s="5" t="n"/>
+      <c r="E248" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F248" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="3" t="n"/>
+      <c r="B249" s="4" t="n"/>
+      <c r="C249" s="5" t="n"/>
+      <c r="D249" s="5" t="n"/>
+      <c r="E249" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F249" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="3" t="n"/>
+      <c r="B250" s="4" t="n"/>
+      <c r="C250" s="5" t="n"/>
+      <c r="D250" s="5" t="n"/>
+      <c r="E250" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F250" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="3" t="n"/>
+      <c r="B251" s="4" t="n"/>
+      <c r="C251" s="5" t="n"/>
+      <c r="D251" s="5" t="n"/>
+      <c r="E251" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F251" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="3" t="n"/>
+      <c r="B252" s="4" t="n"/>
+      <c r="C252" s="5" t="n"/>
+      <c r="D252" s="5" t="n"/>
+      <c r="E252" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F252" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="3" t="n"/>
+      <c r="B253" s="4" t="n"/>
+      <c r="C253" s="5" t="n"/>
+      <c r="D253" s="5" t="n"/>
+      <c r="E253" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F253" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="3" t="n"/>
+      <c r="B254" s="4" t="n"/>
+      <c r="C254" s="5" t="n"/>
+      <c r="D254" s="5" t="n"/>
+      <c r="E254" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F254" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="3" t="n"/>
+      <c r="B255" s="4" t="n"/>
+      <c r="C255" s="5" t="n"/>
+      <c r="D255" s="5" t="n"/>
+      <c r="E255" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F255" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="3" t="n"/>
+      <c r="B256" s="4" t="n"/>
+      <c r="C256" s="5" t="n"/>
+      <c r="D256" s="5" t="n"/>
+      <c r="E256" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F256" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="3" t="n"/>
+      <c r="B257" s="4" t="n"/>
+      <c r="C257" s="5" t="n"/>
+      <c r="D257" s="5" t="n"/>
+      <c r="E257" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F257" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="3" t="n"/>
+      <c r="B258" s="4" t="n"/>
+      <c r="C258" s="5" t="n"/>
+      <c r="D258" s="5" t="n"/>
+      <c r="E258" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F258" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="3" t="n"/>
+      <c r="B259" s="4" t="n"/>
+      <c r="C259" s="5" t="n"/>
+      <c r="D259" s="5" t="n"/>
+      <c r="E259" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F259" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="3" t="n"/>
+      <c r="B260" s="4" t="n"/>
+      <c r="C260" s="5" t="n"/>
+      <c r="D260" s="5" t="n"/>
+      <c r="E260" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F260" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="3" t="n"/>
+      <c r="B261" s="4" t="n"/>
+      <c r="C261" s="5" t="n"/>
+      <c r="D261" s="5" t="n"/>
+      <c r="E261" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F261" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="3" t="n"/>
+      <c r="B262" s="4" t="n"/>
+      <c r="C262" s="5" t="n"/>
+      <c r="D262" s="5" t="n"/>
+      <c r="E262" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F262" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="3" t="n"/>
+      <c r="B263" s="4" t="n"/>
+      <c r="C263" s="5" t="n"/>
+      <c r="D263" s="5" t="n"/>
+      <c r="E263" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F263" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="3" t="n"/>
+      <c r="B264" s="4" t="n"/>
+      <c r="C264" s="5" t="n"/>
+      <c r="D264" s="5" t="n"/>
+      <c r="E264" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F264" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="3" t="n"/>
+      <c r="B265" s="4" t="n"/>
+      <c r="C265" s="5" t="n"/>
+      <c r="D265" s="5" t="n"/>
+      <c r="E265" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F265" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="3" t="n"/>
+      <c r="B266" s="4" t="n"/>
+      <c r="C266" s="5" t="n"/>
+      <c r="D266" s="5" t="n"/>
+      <c r="E266" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F266" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="3" t="n"/>
+      <c r="B267" s="4" t="n"/>
+      <c r="C267" s="5" t="n"/>
+      <c r="D267" s="5" t="n"/>
+      <c r="E267" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F267" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="3" t="n"/>
+      <c r="B268" s="4" t="n"/>
+      <c r="C268" s="5" t="n"/>
+      <c r="D268" s="5" t="n"/>
+      <c r="E268" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F268" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="3" t="n"/>
+      <c r="B269" s="4" t="n"/>
+      <c r="C269" s="5" t="n"/>
+      <c r="D269" s="5" t="n"/>
+      <c r="E269" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F269" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="3" t="n"/>
+      <c r="B270" s="4" t="n"/>
+      <c r="C270" s="5" t="n"/>
+      <c r="D270" s="5" t="n"/>
+      <c r="E270" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F270" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="3" t="n"/>
+      <c r="B271" s="4" t="n"/>
+      <c r="C271" s="5" t="n"/>
+      <c r="D271" s="5" t="n"/>
+      <c r="E271" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F271" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="3" t="n"/>
+      <c r="B272" s="4" t="n"/>
+      <c r="C272" s="5" t="n"/>
+      <c r="D272" s="5" t="n"/>
+      <c r="E272" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F272" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="3" t="n"/>
+      <c r="B273" s="4" t="n"/>
+      <c r="C273" s="5" t="n"/>
+      <c r="D273" s="5" t="n"/>
+      <c r="E273" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F273" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="3" t="n"/>
+      <c r="B274" s="4" t="n"/>
+      <c r="C274" s="5" t="n"/>
+      <c r="D274" s="5" t="n"/>
+      <c r="E274" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F274" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="3" t="n"/>
+      <c r="B275" s="4" t="n"/>
+      <c r="C275" s="5" t="n"/>
+      <c r="D275" s="5" t="n"/>
+      <c r="E275" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F275" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="3" t="n"/>
+      <c r="B276" s="4" t="n"/>
+      <c r="C276" s="5" t="n"/>
+      <c r="D276" s="5" t="n"/>
+      <c r="E276" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F276" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="3" t="n"/>
+      <c r="B277" s="4" t="n"/>
+      <c r="C277" s="5" t="n"/>
+      <c r="D277" s="5" t="n"/>
+      <c r="E277" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F277" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="3" t="n"/>
+      <c r="B278" s="4" t="n"/>
+      <c r="C278" s="5" t="n"/>
+      <c r="D278" s="5" t="n"/>
+      <c r="E278" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F278" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="3" t="n"/>
+      <c r="B279" s="4" t="n"/>
+      <c r="C279" s="5" t="n"/>
+      <c r="D279" s="5" t="n"/>
+      <c r="E279" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F279" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="3" t="n"/>
+      <c r="B280" s="4" t="n"/>
+      <c r="C280" s="5" t="n"/>
+      <c r="D280" s="5" t="n"/>
+      <c r="E280" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F280" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="3" t="n"/>
+      <c r="B281" s="4" t="n"/>
+      <c r="C281" s="5" t="n"/>
+      <c r="D281" s="5" t="n"/>
+      <c r="E281" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F281" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="3" t="n"/>
+      <c r="B282" s="4" t="n"/>
+      <c r="C282" s="5" t="n"/>
+      <c r="D282" s="5" t="n"/>
+      <c r="E282" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F282" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="3" t="n"/>
+      <c r="B283" s="4" t="n"/>
+      <c r="C283" s="5" t="n"/>
+      <c r="D283" s="5" t="n"/>
+      <c r="E283" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F283" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="3" t="n"/>
+      <c r="B284" s="4" t="n"/>
+      <c r="C284" s="5" t="n"/>
+      <c r="D284" s="5" t="n"/>
+      <c r="E284" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F284" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="3" t="n"/>
+      <c r="B285" s="4" t="n"/>
+      <c r="C285" s="5" t="n"/>
+      <c r="D285" s="5" t="n"/>
+      <c r="E285" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F285" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="3" t="n"/>
+      <c r="B286" s="4" t="n"/>
+      <c r="C286" s="5" t="n"/>
+      <c r="D286" s="5" t="n"/>
+      <c r="E286" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F286" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="3" t="n"/>
+      <c r="B287" s="4" t="n"/>
+      <c r="C287" s="5" t="n"/>
+      <c r="D287" s="5" t="n"/>
+      <c r="E287" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F287" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="3" t="n"/>
+      <c r="B288" s="4" t="n"/>
+      <c r="C288" s="5" t="n"/>
+      <c r="D288" s="5" t="n"/>
+      <c r="E288" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F288" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="3" t="n"/>
+      <c r="B289" s="4" t="n"/>
+      <c r="C289" s="5" t="n"/>
+      <c r="D289" s="5" t="n"/>
+      <c r="E289" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F289" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="3" t="n"/>
+      <c r="B290" s="4" t="n"/>
+      <c r="C290" s="5" t="n"/>
+      <c r="D290" s="5" t="n"/>
+      <c r="E290" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F290" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="3" t="n"/>
+      <c r="B291" s="4" t="n"/>
+      <c r="C291" s="5" t="n"/>
+      <c r="D291" s="5" t="n"/>
+      <c r="E291" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F291" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="3" t="n"/>
+      <c r="B292" s="4" t="n"/>
+      <c r="C292" s="5" t="n"/>
+      <c r="D292" s="5" t="n"/>
+      <c r="E292" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F292" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="3" t="n"/>
+      <c r="B293" s="4" t="n"/>
+      <c r="C293" s="5" t="n"/>
+      <c r="D293" s="5" t="n"/>
+      <c r="E293" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F293" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="3" t="n"/>
+      <c r="B294" s="4" t="n"/>
+      <c r="C294" s="5" t="n"/>
+      <c r="D294" s="5" t="n"/>
+      <c r="E294" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F294" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="3" t="n"/>
+      <c r="B295" s="4" t="n"/>
+      <c r="C295" s="5" t="n"/>
+      <c r="D295" s="5" t="n"/>
+      <c r="E295" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F295" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="3" t="n"/>
+      <c r="B296" s="4" t="n"/>
+      <c r="C296" s="5" t="n"/>
+      <c r="D296" s="5" t="n"/>
+      <c r="E296" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F296" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="3" t="n"/>
+      <c r="B297" s="4" t="n"/>
+      <c r="C297" s="5" t="n"/>
+      <c r="D297" s="5" t="n"/>
+      <c r="E297" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F297" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="3" t="n"/>
+      <c r="B298" s="4" t="n"/>
+      <c r="C298" s="5" t="n"/>
+      <c r="D298" s="5" t="n"/>
+      <c r="E298" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F298" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="3" t="n"/>
+      <c r="B299" s="4" t="n"/>
+      <c r="C299" s="5" t="n"/>
+      <c r="D299" s="5" t="n"/>
+      <c r="E299" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F299" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="3" t="n"/>
+      <c r="B300" s="4" t="n"/>
+      <c r="C300" s="5" t="n"/>
+      <c r="D300" s="5" t="n"/>
+      <c r="E300" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F300" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="3" t="n"/>
+      <c r="B301" s="4" t="n"/>
+      <c r="C301" s="5" t="n"/>
+      <c r="D301" s="5" t="n"/>
+      <c r="E301" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+      <c r="F301" s="6" t="inlineStr">
+        <is>
+          <t>تلقائي</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
+  <dataValidations count="3">
+    <dataValidation sqref="C2:C301" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="الصف" error="اختر الصف من القائمة." type="list">
+      <formula1>'قوائم'!$A$1:$A$14</formula1>
+    </dataValidation>
+    <dataValidation sqref="D2:D301" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="الشعبة" error="اختر الشعبة: 1 أو 2 أو 3 أو 4." type="list">
+      <formula1>'قوائم'!$B$1:$B$4</formula1>
+    </dataValidation>
+    <dataValidation sqref="B2:B301" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="رقم الهاتف" error="رقم الهاتف يجب أن يتكون من 8 أرقام." type="custom">
+      <formula1>AND(LEN(B2)=8,ISNUMBER(--B2))</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>روضة</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>تمهيدي</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>الصف الأول</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>الصف الثاني</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>الصف الثالث</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>الصف الرابع</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>الصف الخامس</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>الصف السادس</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>الصف السابع</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>الصف الثامن</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>الصف التاسع</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>الصف العاشر</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>الصف الحادي عشر</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>الصف الثاني عشر</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>نموذج استيراد المعلمين — منصة جود</t>
+        </is>
+      </c>
+      <c r="B1" s="10" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="11" t="inlineStr"/>
+      <c r="B2" s="10" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>العمود</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>طريقة التعبئة</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>اسم المعلم</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>اكتب الاسم الكامل (مطلوب).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>رقم الهاتف</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>البريد الإلكتروني</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>كلمة المرور</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>المادة</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>الصفوف والشعب</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>سالم علي</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>92345678</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>salem@example.com</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>12345678</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>الرياضيات</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>الحلقة الأولى — الصف الأول — الشعبة (أ)</t>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>8 أرقام بدون مفتاح الدولة (مطلوب).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>الصف</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>اختر من القائمة المنسدلة: الروضة، التمهيدي، أو من الصف الأول إلى الثاني عشر.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>الشعبة</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>اختر من القائمة المنسدلة: 1، 2، 3، 4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>اسم المستخدم</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>لا تكتب شيئًا: تُنشئ المنصة رقمًا فريدًا من 6 أرقام لكل معلم تلقائيًا.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>الرقم السري</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>لا تكتب شيئًا: يُعيَّن تلقائيًا 123456 ويستطيع المعلم تغييره من ملفه الشخصي.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr"/>
+      <c r="B10" s="10" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>معلم يدرّس أكثر من صف أو شعبة</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>كرّر اسمه ورقم هاتفه في سطر لكل صف/شعبة، وسيُنشأ له حساب واحد يشمل كل صفوفه.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr"/>
+      <c r="B12" s="10" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>مثال (لا تنسخه إلى ورقة المعلمين):</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>اسم المعلم | رقم الهاتف | الصف | الشعبة</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>سالم علي الهنائي | 92345678 | الصف الأول | 2</t>
         </is>
       </c>
     </row>

--- a/teacher_import_template.xlsx
+++ b/teacher_import_template.xlsx
@@ -5403,7 +5403,7 @@
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <dataValidations count="3">
     <dataValidation sqref="C2:C301" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="الصف" error="اختر الصف من القائمة." type="list">
-      <formula1>'قوائم'!$A$1:$A$14</formula1>
+      <formula1>'قوائم'!$A$1:$A$6</formula1>
     </dataValidation>
     <dataValidation sqref="D2:D301" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="الشعبة" error="اختر الشعبة: 1 أو 2 أو 3 أو 4." type="list">
       <formula1>'قوائم'!$B$1:$B$4</formula1>
@@ -5423,7 +5423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5489,61 +5489,34 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>الصف الخامس</t>
-        </is>
-      </c>
+      <c r="A7" s="7" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>الصف السادس</t>
-        </is>
-      </c>
+      <c r="A8" s="7" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>الصف السابع</t>
-        </is>
-      </c>
+      <c r="A9" s="7" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>الصف الثامن</t>
-        </is>
-      </c>
+      <c r="A10" s="7" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>الصف التاسع</t>
-        </is>
-      </c>
+      <c r="A11" s="7" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>الصف العاشر</t>
-        </is>
-      </c>
+      <c r="A12" s="7" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>الصف الحادي عشر</t>
-        </is>
-      </c>
+      <c r="A13" s="7" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>الصف الثاني عشر</t>
-        </is>
-      </c>
-    </row>
+      <c r="A14" s="7" t="n"/>
+    </row>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5618,7 +5591,7 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>اختر من القائمة المنسدلة: الروضة، التمهيدي، أو من الصف الأول إلى الثاني عشر.</t>
+          <t>اختر من القائمة المنسدلة: روضة، تمهيدي، الصف الأول، الصف الثاني، الصف الثالث، الصف الرابع.</t>
         </is>
       </c>
     </row>
